--- a/artfynd/A 17107-2026 artfynd.xlsx
+++ b/artfynd/A 17107-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93799401</v>
+        <v>91297819</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Måcksjön, SO-sidan, vid källa, Gstr</t>
+          <t>Måcksjön, sydändan, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578286</v>
+        <v>578279</v>
       </c>
       <c r="R2" t="n">
-        <v>6751053</v>
+        <v>6751029</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Källa, Blandskog, där källa rinner fram, fuktig mark med vitmossa  i botten</t>
+          <t>Skog, Blandskog, fuktig grandominerad skog i bergsluttning, källa utströmning, vitmossor, örter o ormbunkar</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 279011N</t>
+          <t>Gst Fyndnr 284144L</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -771,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Ståhl, Birgitta Hellström</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,7 +789,7 @@
         <v>93799409</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,6 +890,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>93799401</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Måcksjön, SO-sidan, vid källa, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578286</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6751053</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-08-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-08-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Källa, Blandskog, där källa rinner fram, fuktig mark med vitmossa  i botten</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 279011N</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Peter Ståhl, Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>
